--- a/dados/gerencial/consolidado_gerencial_2021.xlsx
+++ b/dados/gerencial/consolidado_gerencial_2021.xlsx
@@ -497,13 +497,13 @@
         <v>48</v>
       </c>
       <c r="E4" t="n">
-        <v>392831.07</v>
+        <v>393880.58</v>
       </c>
       <c r="F4" t="n">
-        <v>248384.74</v>
+        <v>249384.78</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>44239</v>
+        <v>44236</v>
       </c>
     </row>
     <row r="5">
@@ -519,16 +519,16 @@
         <v>49</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>214964.31</v>
+        <v>214194.5</v>
       </c>
       <c r="F5" t="n">
-        <v>139812.4</v>
+        <v>140354.12</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>44235</v>
+        <v>44239</v>
       </c>
     </row>
     <row r="6">
@@ -547,13 +547,13 @@
         <v>45</v>
       </c>
       <c r="E6" t="n">
-        <v>445726.3</v>
+        <v>446332.87</v>
       </c>
       <c r="F6" t="n">
-        <v>279257.28</v>
+        <v>280537.05</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>44266</v>
+        <v>44270</v>
       </c>
     </row>
     <row r="7">
@@ -572,10 +572,10 @@
         <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>214496.03</v>
+        <v>213698.88</v>
       </c>
       <c r="F7" t="n">
-        <v>130280.85</v>
+        <v>130105.36</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>44270</v>
@@ -597,10 +597,10 @@
         <v>52</v>
       </c>
       <c r="E8" t="n">
-        <v>500719.91</v>
+        <v>499795.2</v>
       </c>
       <c r="F8" t="n">
-        <v>340841.2</v>
+        <v>338984.06</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>44298</v>
@@ -622,13 +622,13 @@
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>197276.63</v>
+        <v>197983.51</v>
       </c>
       <c r="F9" t="n">
-        <v>130009.15</v>
+        <v>129557.63</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>44301</v>
+        <v>44298</v>
       </c>
     </row>
     <row r="10">
@@ -641,16 +641,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D10" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E10" t="n">
-        <v>506363.93</v>
+        <v>505380.76</v>
       </c>
       <c r="F10" t="n">
-        <v>320578.98</v>
+        <v>321239.83</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>44326</v>
@@ -672,13 +672,13 @@
         <v>4</v>
       </c>
       <c r="E11" t="n">
-        <v>199529.5</v>
+        <v>199321.54</v>
       </c>
       <c r="F11" t="n">
-        <v>130441.22</v>
+        <v>128540.18</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>44328</v>
+        <v>44326</v>
       </c>
     </row>
     <row r="12">
@@ -694,16 +694,16 @@
         <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E12" t="n">
-        <v>589973.71</v>
+        <v>590818.24</v>
       </c>
       <c r="F12" t="n">
-        <v>391158.31</v>
+        <v>391383.01</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>44361</v>
+        <v>44362</v>
       </c>
     </row>
     <row r="13">
@@ -722,13 +722,13 @@
         <v>7</v>
       </c>
       <c r="E13" t="n">
-        <v>202964.18</v>
+        <v>203395.2</v>
       </c>
       <c r="F13" t="n">
-        <v>135119.24</v>
+        <v>133833.49</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>44357</v>
+        <v>44361</v>
       </c>
     </row>
     <row r="14">
@@ -741,19 +741,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D14" t="n">
         <v>61</v>
       </c>
       <c r="E14" t="n">
-        <v>608535.73</v>
+        <v>609329.46</v>
       </c>
       <c r="F14" t="n">
-        <v>396153.61</v>
+        <v>401205.53</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>44386</v>
+        <v>44391</v>
       </c>
     </row>
     <row r="15">
@@ -772,13 +772,13 @@
         <v>10</v>
       </c>
       <c r="E15" t="n">
-        <v>242346.22</v>
+        <v>241310.67</v>
       </c>
       <c r="F15" t="n">
-        <v>156101.48</v>
+        <v>155137.06</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>44389</v>
+        <v>44390</v>
       </c>
     </row>
     <row r="16">
@@ -797,13 +797,13 @@
         <v>66</v>
       </c>
       <c r="E16" t="n">
-        <v>594748.52</v>
+        <v>594859.95</v>
       </c>
       <c r="F16" t="n">
-        <v>403311.89</v>
+        <v>404976.3</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>44417</v>
+        <v>44424</v>
       </c>
     </row>
     <row r="17">
@@ -822,13 +822,13 @@
         <v>11</v>
       </c>
       <c r="E17" t="n">
-        <v>238044.78</v>
+        <v>236804.44</v>
       </c>
       <c r="F17" t="n">
-        <v>157288.82</v>
+        <v>156474.79</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>44418</v>
+        <v>44424</v>
       </c>
     </row>
     <row r="18">
@@ -847,13 +847,13 @@
         <v>77</v>
       </c>
       <c r="E18" t="n">
-        <v>707027.08</v>
+        <v>708108.73</v>
       </c>
       <c r="F18" t="n">
-        <v>483900.9</v>
+        <v>486486.91</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>44452</v>
+        <v>44454</v>
       </c>
     </row>
     <row r="19">
@@ -872,13 +872,13 @@
         <v>8</v>
       </c>
       <c r="E19" t="n">
-        <v>233944.24</v>
+        <v>232341.99</v>
       </c>
       <c r="F19" t="n">
-        <v>150080.2</v>
+        <v>148252.63</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>44449</v>
+        <v>44454</v>
       </c>
     </row>
     <row r="20">
@@ -897,10 +897,10 @@
         <v>78</v>
       </c>
       <c r="E20" t="n">
-        <v>799917.83</v>
+        <v>801893.8100000001</v>
       </c>
       <c r="F20" t="n">
-        <v>543975.99</v>
+        <v>548978.4</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>44480</v>
@@ -922,10 +922,10 @@
         <v>7</v>
       </c>
       <c r="E21" t="n">
-        <v>237175.97</v>
+        <v>236030.17</v>
       </c>
       <c r="F21" t="n">
-        <v>149205.44</v>
+        <v>148141.46</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>44481</v>
@@ -947,13 +947,13 @@
         <v>106</v>
       </c>
       <c r="E22" t="n">
-        <v>947867.2</v>
+        <v>948208.6899999999</v>
       </c>
       <c r="F22" t="n">
-        <v>651460.21</v>
+        <v>653215.14</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>44510</v>
+        <v>44511</v>
       </c>
     </row>
     <row r="23">
@@ -972,13 +972,13 @@
         <v>15</v>
       </c>
       <c r="E23" t="n">
-        <v>253771.86</v>
+        <v>254223.5</v>
       </c>
       <c r="F23" t="n">
-        <v>160746.03</v>
+        <v>160364.92</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>44512</v>
+        <v>44511</v>
       </c>
     </row>
     <row r="24">
@@ -997,13 +997,13 @@
         <v>107</v>
       </c>
       <c r="E24" t="n">
-        <v>1136291.43</v>
+        <v>1135166.18</v>
       </c>
       <c r="F24" t="n">
-        <v>775869.23</v>
+        <v>778171.65</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>44545</v>
+        <v>44543</v>
       </c>
     </row>
     <row r="25">
@@ -1022,13 +1022,13 @@
         <v>9</v>
       </c>
       <c r="E25" t="n">
-        <v>303441.49</v>
+        <v>304505.49</v>
       </c>
       <c r="F25" t="n">
-        <v>193690.47</v>
+        <v>194024.1</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>44543</v>
+        <v>44544</v>
       </c>
     </row>
     <row r="26">
@@ -1047,10 +1047,10 @@
         <v>97</v>
       </c>
       <c r="E26" t="n">
-        <v>1036238.16</v>
+        <v>1035554.48</v>
       </c>
       <c r="F26" t="n">
-        <v>734514.46</v>
+        <v>732765.5</v>
       </c>
       <c r="G26" s="3" t="n">
         <v>44572</v>
@@ -1072,10 +1072,10 @@
         <v>32</v>
       </c>
       <c r="E27" t="n">
-        <v>346319.15</v>
+        <v>347586.75</v>
       </c>
       <c r="F27" t="n">
-        <v>224637.19</v>
+        <v>225869.37</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>44571</v>
@@ -1088,13 +1088,13 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="E28" t="n">
-        <v>11150515.23</v>
+        <v>11150725.59</v>
       </c>
       <c r="F28" t="n">
-        <v>7426819.29</v>
+        <v>7437983.27</v>
       </c>
     </row>
   </sheetData>
